--- a/ksoft_old/docs/stock/Bestand_Impregnated_Paper_Set_up_details.xlsx
+++ b/ksoft_old/docs/stock/Bestand_Impregnated_Paper_Set_up_details.xlsx
@@ -26492,13 +26492,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF7B587C-BDD2-4CCE-B29D-124BFBAEB3B9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06E3C21C-7DC7-457F-BCCF-38FF2D93E2D1}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1763F15D-A7AD-4169-90DD-0681ED645493}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ECBE8C3D-7FA8-46DC-8344-7B817495CF14}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B394A85D-787B-4DC9-B10E-2793FD43A512}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52F82C4D-00B4-41C4-93E6-1A7E0DA01458}"/>
 </file>
--- a/ksoft_old/docs/stock/Bestand_Impregnated_Paper_Set_up_details.xlsx
+++ b/ksoft_old/docs/stock/Bestand_Impregnated_Paper_Set_up_details.xlsx
@@ -26492,13 +26492,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06E3C21C-7DC7-457F-BCCF-38FF2D93E2D1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F5FF5B8-371A-4309-9E8A-2B42A70AE4E9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ECBE8C3D-7FA8-46DC-8344-7B817495CF14}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4548BFA-CD5C-4137-9FFA-74B10BB35286}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52F82C4D-00B4-41C4-93E6-1A7E0DA01458}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76685F3B-F5DF-4FE8-8129-550F03A47A3F}"/>
 </file>
--- a/ksoft_old/docs/stock/Bestand_Impregnated_Paper_Set_up_details.xlsx
+++ b/ksoft_old/docs/stock/Bestand_Impregnated_Paper_Set_up_details.xlsx
@@ -26492,13 +26492,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F5FF5B8-371A-4309-9E8A-2B42A70AE4E9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF7B587C-BDD2-4CCE-B29D-124BFBAEB3B9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4548BFA-CD5C-4137-9FFA-74B10BB35286}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1763F15D-A7AD-4169-90DD-0681ED645493}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76685F3B-F5DF-4FE8-8129-550F03A47A3F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B394A85D-787B-4DC9-B10E-2793FD43A512}"/>
 </file>